--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AntigravityProject\Project\shuangxiu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF869172-CE43-4D3A-9A34-809F4C7D9D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F973D3A0-9E10-4B13-8D45-8BB347761619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t>公司名称</t>
   </si>
@@ -262,6 +262,22 @@
   </si>
   <si>
     <t>1.示例a。2.示例b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例公司2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>严格双休</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.示例c。2.示例d</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -646,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
@@ -928,6 +944,23 @@
         <v>68</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
